--- a/artfynd/A 33051-2021 artfynd.xlsx
+++ b/artfynd/A 33051-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33051-2021 artfynd.xlsx
+++ b/artfynd/A 33051-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56164645</v>
+        <v>62555405</v>
       </c>
       <c r="B2" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232138</v>
+        <v>473</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683070.9810177279</v>
+        <v>683005</v>
       </c>
       <c r="R2" t="n">
-        <v>6685241.442553204</v>
+        <v>6685370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca. 100 ex. i barrmatta med gles vegetation av vispstarr, i en 40-årig granplantering.</t>
+          <t>3 ex. under björk och gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>40-årig granplantering.</t>
+          <t>Äldre, örtrik granskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,47 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62555412</v>
+        <v>62555437</v>
       </c>
       <c r="B3" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3674</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682980.1323945934</v>
+        <v>683055</v>
       </c>
       <c r="R3" t="n">
-        <v>6685325.363263231</v>
+        <v>6685296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,27 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-08-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca. 10 ex.</t>
+          <t>2 dm2 i barrmatta under gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +886,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av asp och björk.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62555493</v>
+        <v>62555417</v>
       </c>
       <c r="B4" t="n">
-        <v>90366</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5836</v>
+        <v>1988</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -981,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682963.9312024063</v>
+        <v>683006</v>
       </c>
       <c r="R4" t="n">
-        <v>6685429.929221237</v>
+        <v>6685378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,21 +984,11 @@
           <t>2004-08-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2004-08-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2 ex.</t>
@@ -1042,6 +1002,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av asp och björk.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1058,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62555424</v>
+        <v>75968027</v>
       </c>
       <c r="B5" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,46 +1034,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4189</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+          <t>NW om Assjö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683085.9306994075</v>
+        <v>683028</v>
       </c>
       <c r="R5" t="n">
-        <v>6685241.199000483</v>
+        <v>6685334</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,27 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca. 10 gamla fruktkroppar i barrmatta, i en 40-årig granplantering.</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,26 +1105,1410 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>40-årig granplantering.</t>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Martin Gotink</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Gotink</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Gotink</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>62555412</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>682980</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6685325</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>62555416</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>683031</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6685341</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ex. i äldre, grandomierad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>62555424</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>683086</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6685241</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca. 10 gamla fruktkroppar i barrmatta, i en 40-årig granplantering.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>40-årig granplantering.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>62555428</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>683065</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6685296</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca. 200 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av lövträd.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>62555429</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>683055</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6685296</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2011-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2011-09-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca. 30 ex. i barrmatta och mossvegetation.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av asp och björk.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>75891338</v>
+      </c>
+      <c r="B11" t="n">
+        <v>89138</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4404</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sotvaxskivling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hygrophorus camarophyllus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>683065</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6685296</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2011-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2011-09-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av asp och björk.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>62555485</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>683090</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6685302</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av lövträd.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>62555486</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>683025</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6685350</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>62555493</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92928</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>682964</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6685430</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>56164645</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>683071</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6685241</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca. 100 ex. i barrmatta med gles vegetation av vispstarr, i en 40-årig granplantering.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>40-årig granplantering.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>62555481</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91433</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>233196</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fjällfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>683010</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6685361</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2011-09-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2011-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>6 ex., under gran, dels i barrmatta, dels i vegetationsskikt av mossor, blåsippa, ekorrbär och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av asp och björk.</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>62555475</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>683061</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6685307</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En häxring, 3 m i diameter, under äldre gran och asp.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av asp och björk.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
